--- a/excel_db/instructors.xlsx
+++ b/excel_db/instructors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -38,30 +38,6 @@
   </si>
   <si>
     <t>created_at</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>INST-0001</t>
-  </si>
-  <si>
-    <t>ISAAC OKYERE</t>
-  </si>
-  <si>
-    <t>socatoa</t>
-  </si>
-  <si>
-    <t>scrypt:32768:8:1$49xktcoWGbuB1s3D$297dea0330dc36138b33b093adfd76c62fc8a044bfbaa129c8bd08e1359468306a35d21282cff94124b1a678a909de928aa0893d0d397628bcdea5fb503d5218</t>
-  </si>
-  <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t>2026-06-06 01:45:33</t>
-  </si>
-  <si>
-    <t>General Science</t>
   </si>
 </sst>
 </file>
@@ -419,10 +395,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -446,35 +422,6 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/excel_db/instructors.xlsx
+++ b/excel_db/instructors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -38,6 +38,30 @@
   </si>
   <si>
     <t>created_at</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>INST-0001</t>
+  </si>
+  <si>
+    <t>ISAAC OKYERE</t>
+  </si>
+  <si>
+    <t>socatoa</t>
+  </si>
+  <si>
+    <t>scrypt:32768:8:1$ipkOtvwdJsOdpOcy$7a84c58edcc895609e08ddc0cabc4931a5a42da378d9a1756bc3eb6d42da7031b8dd6e0d33f08525de3d449edec3245693c4bd1a8ed72d8ed25a9eb694bc3e21</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>2026-06-06 10:34:53</t>
+  </si>
+  <si>
+    <t>General Science</t>
   </si>
 </sst>
 </file>
@@ -395,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,6 +446,35 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/excel_db/instructors.xlsx
+++ b/excel_db/instructors.xlsx
@@ -52,13 +52,13 @@
     <t>socatoa</t>
   </si>
   <si>
-    <t>scrypt:32768:8:1$ipkOtvwdJsOdpOcy$7a84c58edcc895609e08ddc0cabc4931a5a42da378d9a1756bc3eb6d42da7031b8dd6e0d33f08525de3d449edec3245693c4bd1a8ed72d8ed25a9eb694bc3e21</t>
+    <t>scrypt:32768:8:1$5vkhfLH5K7FbrlIH$802a9fcb7c407ae69a1448e7c3bdd399cbbbb09fdce9aa9f43437ac17eb49381f6fe9dc431c2373e51cab19e839a2c886067e12721f54a656e42d1e51942448c</t>
   </si>
   <si>
     <t>Science</t>
   </si>
   <si>
-    <t>2026-06-06 10:34:53</t>
+    <t>2026-06-11 08:25:06</t>
   </si>
   <si>
     <t>General Science</t>
